--- a/QA-Assignment/Manual Testing.xlsx
+++ b/QA-Assignment/Manual Testing.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9708" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9708" firstSheet="5" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -1545,7 +1545,7 @@
     <t>If applicable, multiple reference cards are shown, each linking to a distinct source page</t>
   </si>
   <si>
-    <t>Only one citation was displayed for a broad query instead of multiple citations.</t>
+    <t>Multiple citation was displayed for a broad query</t>
   </si>
   <si>
     <t>TC-SM-001</t>
@@ -1637,7 +1637,7 @@
     <t>Second tab reflects the logged-in state without requiring re-login</t>
   </si>
   <si>
-    <t>User is redirected to the login page in the second browser tab instead of accessing the existing logged-in session.</t>
+    <t>User is redirected to the same page in the second browser tab and  accessing the existing logged-in session.</t>
   </si>
   <si>
     <t>TC-SM-005</t>
@@ -7026,8 +7026,8 @@
       <c r="K6" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="L6" s="8" t="s">
-        <v>96</v>
+      <c r="L6" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -7244,8 +7244,8 @@
       <c r="K5" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="L5" s="8" t="s">
-        <v>96</v>
+      <c r="L5" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:12">
